--- a/backend/enquiries.xlsx
+++ b/backend/enquiries.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -625,6 +625,38 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-02 14:39:30</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Nimal Sundar</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>9360038489</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sri sankara </t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CBSE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
